--- a/output/graficos_nacionales/plot_nacional_regiones_e_mediabrut_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_e_mediabrut_a_2024.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:30</t>
+    <t xml:space="preserve">2026-09-09 21:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_e_mediabrut_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_e_mediabrut_a_2024.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:24</t>
+    <t xml:space="preserve">2026-09-18 12:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_e_mediabrut_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_e_mediabrut_a_2024.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 12:17</t>
+    <t xml:space="preserve">2026-10-05 19:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -586,7 +586,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>102.53</v>
+        <v>102.54</v>
       </c>
     </row>
     <row r="15">
